--- a/public/templates/careplan2_template.xlsx
+++ b/public/templates/careplan2_template.xlsx
@@ -11,24 +11,25 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="15">
-  <si>
-    <t>居宅サービス計画書（2）</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
   <si>
     <t>作成年月日</t>
   </si>
   <si>
+    <t xml:space="preserve">　　年　月　日</t>
+  </si>
+  <si>
+    <t>居宅サービス計画書（２）</t>
+  </si>
+  <si>
     <t>利用者名</t>
   </si>
   <si>
-    <t>様</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>生活全般の解決すべき課題(ニーズ)</t>
+    <t xml:space="preserve">　　　　　　　　　　　　様</t>
+  </si>
+  <si>
+    <t xml:space="preserve">生活全般の解決すべき課題
+（ニーズ）</t>
   </si>
   <si>
     <t>目標</t>
@@ -40,7 +41,7 @@
     <t>長期目標</t>
   </si>
   <si>
-    <t>(期間)</t>
+    <t>（期間）</t>
   </si>
   <si>
     <t>短期目標</t>
@@ -56,13 +57,16 @@
   </si>
   <si>
     <t>期間</t>
+  </si>
+  <si>
+    <t>※本計画書はAIによる支援原案です。適切なアセスメントに基づき、介護支援専門員が最終的な確認・修正を行ってください。</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -73,22 +77,50 @@
     <font>
       <b/>
       <sz val="16"/>
+      <name val="MS PGothic"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="MS PGothic"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="MS PGothic"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FFFF0000"/>
+      <sz val="9"/>
+      <name val="MS PGothic"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0E0E0"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -102,13 +134,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -448,280 +486,257 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:P15"/>
+  <dimension ref="B1:J22"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="2" customWidth="1"/>
-    <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="5" max="5" width="2" customWidth="1"/>
-    <col min="6" max="6" width="10" customWidth="1"/>
-    <col min="7" max="7" width="20" customWidth="1"/>
-    <col min="8" max="8" width="2" customWidth="1"/>
-    <col min="9" max="9" width="10" customWidth="1"/>
-    <col min="10" max="10" width="25" customWidth="1"/>
-    <col min="11" max="11" width="2" customWidth="1"/>
-    <col min="12" max="12" width="15" customWidth="1"/>
-    <col min="13" max="13" width="2" customWidth="1"/>
-    <col min="14" max="14" width="10" customWidth="1"/>
-    <col min="15" max="15" width="2" customWidth="1"/>
-    <col min="16" max="16" width="15" customWidth="1"/>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="8" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
+    <col min="6" max="6" width="8" customWidth="1"/>
+    <col min="7" max="7" width="30" customWidth="1"/>
+    <col min="8" max="8" width="15" customWidth="1"/>
+    <col min="9" max="10" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E2" s="1" t="s">
+    <row r="1" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I1" t="s">
         <v>0</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>2</v>
-      </c>
-      <c r="E4" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="C4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="2" t="s">
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="J6" s="2" t="s">
+      <c r="D6"/>
+      <c r="E6"/>
+      <c r="F6"/>
+      <c r="G6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="K6" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="O6" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="P6" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" s="2" t="s">
+      <c r="H6"/>
+      <c r="I6"/>
+      <c r="J6"/>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B7" s="3"/>
+      <c r="C7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F7" s="2" t="s">
+      <c r="D7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="E7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="I7" s="2" t="s">
+      <c r="F7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="G7" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="L7" s="2" t="s">
+      <c r="H7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="N7" s="2" t="s">
+      <c r="I7" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="P7" s="2" t="s">
+      <c r="J7" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3"/>
-      <c r="O8" s="3"/>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" ht="60" customHeight="1" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="3"/>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" ht="60" customHeight="1" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
-      <c r="N10" s="3"/>
-      <c r="O10" s="3"/>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" ht="60" customHeight="1" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="3"/>
-      <c r="P11" s="3"/>
-    </row>
-    <row r="12" ht="60" customHeight="1" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="3"/>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" ht="60" customHeight="1" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="3"/>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" ht="60" customHeight="1" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
-      <c r="N14" s="3"/>
-      <c r="O14" s="3"/>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" ht="60" customHeight="1" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
-      <c r="N15" s="3"/>
-      <c r="O15" s="3"/>
-      <c r="P15" s="3"/>
+    <row r="8" ht="80" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+    </row>
+    <row r="9" ht="80" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+    </row>
+    <row r="10" ht="80" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+    </row>
+    <row r="11" ht="80" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+    </row>
+    <row r="12" ht="80" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+    </row>
+    <row r="13" ht="80" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+    </row>
+    <row r="14" ht="80" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+    </row>
+    <row r="15" ht="80" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+    </row>
+    <row r="16" ht="80" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+    </row>
+    <row r="17" ht="80" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+    </row>
+    <row r="18" ht="80" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+    </row>
+    <row r="19" ht="80" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+    </row>
+    <row r="20" ht="80" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B22" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
     </row>
   </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B2:J2"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="G6:J6"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B22:J22"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/public/templates/careplan2_template.xlsx
+++ b/public/templates/careplan2_template.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
   <si>
     <t>作成年月日</t>
   </si>
@@ -25,7 +25,7 @@
     <t>利用者名</t>
   </si>
   <si>
-    <t xml:space="preserve">　　　　　　　　　　　　様</t>
+    <t xml:space="preserve">　　　　　　　　　　様</t>
   </si>
   <si>
     <t xml:space="preserve">生活全般の解決すべき課題
@@ -57,16 +57,13 @@
   </si>
   <si>
     <t>期間</t>
-  </si>
-  <si>
-    <t>※本計画書はAIによる支援原案です。適切なアセスメントに基づき、介護支援専門員が最終的な確認・修正を行ってください。</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -80,18 +77,11 @@
       <name val="MS PGothic"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="MS PGothic"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="MS PGothic"/>
-    </font>
-    <font>
-      <i/>
-      <color rgb="FFFF0000"/>
-      <sz val="9"/>
       <name val="MS PGothic"/>
     </font>
   </fonts>
@@ -134,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -144,9 +134,8 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" indent="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -486,29 +475,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:J22"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B1:K20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="25" customWidth="1"/>
-    <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="8" customWidth="1"/>
-    <col min="5" max="5" width="22" customWidth="1"/>
-    <col min="6" max="6" width="8" customWidth="1"/>
-    <col min="7" max="7" width="30" customWidth="1"/>
-    <col min="8" max="8" width="15" customWidth="1"/>
-    <col min="9" max="10" width="12" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="5" max="5" width="8" customWidth="1"/>
+    <col min="6" max="6" width="22" customWidth="1"/>
+    <col min="7" max="7" width="8" customWidth="1"/>
+    <col min="8" max="8" width="35" customWidth="1"/>
+    <col min="9" max="9" width="15" customWidth="1"/>
+    <col min="10" max="11" width="10" customWidth="1"/>
+    <col min="12" max="12" width="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="9:10" x14ac:dyDescent="0.25">
-      <c r="I1" t="s">
+    <row r="1" spans="10:11" x14ac:dyDescent="0.25">
+      <c r="J1" t="s">
         <v>0</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
@@ -520,60 +514,65 @@
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
-    </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="K2" s="1"/>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6"/>
+      <c r="D6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D6"/>
       <c r="E6"/>
       <c r="F6"/>
-      <c r="G6" s="3" t="s">
+      <c r="G6"/>
+      <c r="H6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H6"/>
       <c r="I6"/>
       <c r="J6"/>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B7" s="3"/>
-      <c r="C7" s="3" t="s">
+      <c r="K6"/>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B7"/>
+      <c r="C7"/>
+      <c r="D7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="E7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="F7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="G7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="H7" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="I7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J7" s="3" t="s">
+      <c r="K7" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="8" ht="80" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="8" ht="100" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
@@ -583,8 +582,9 @@
       <c r="H8" s="4"/>
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
-    </row>
-    <row r="9" ht="80" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K8" s="4"/>
+    </row>
+    <row r="9" ht="100" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
@@ -594,8 +594,9 @@
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
       <c r="J9" s="4"/>
-    </row>
-    <row r="10" ht="80" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K9" s="4"/>
+    </row>
+    <row r="10" ht="100" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -605,8 +606,9 @@
       <c r="H10" s="4"/>
       <c r="I10" s="4"/>
       <c r="J10" s="4"/>
-    </row>
-    <row r="11" ht="80" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K10" s="4"/>
+    </row>
+    <row r="11" ht="100" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
@@ -616,8 +618,9 @@
       <c r="H11" s="4"/>
       <c r="I11" s="4"/>
       <c r="J11" s="4"/>
-    </row>
-    <row r="12" ht="80" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K11" s="4"/>
+    </row>
+    <row r="12" ht="100" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
@@ -627,8 +630,9 @@
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
-    </row>
-    <row r="13" ht="80" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K12" s="4"/>
+    </row>
+    <row r="13" ht="100" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
@@ -638,8 +642,9 @@
       <c r="H13" s="4"/>
       <c r="I13" s="4"/>
       <c r="J13" s="4"/>
-    </row>
-    <row r="14" ht="80" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K13" s="4"/>
+    </row>
+    <row r="14" ht="100" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
@@ -649,8 +654,9 @@
       <c r="H14" s="4"/>
       <c r="I14" s="4"/>
       <c r="J14" s="4"/>
-    </row>
-    <row r="15" ht="80" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K14" s="4"/>
+    </row>
+    <row r="15" ht="100" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
@@ -660,8 +666,9 @@
       <c r="H15" s="4"/>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
-    </row>
-    <row r="16" ht="80" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K15" s="4"/>
+    </row>
+    <row r="16" ht="100" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
@@ -671,8 +678,9 @@
       <c r="H16" s="4"/>
       <c r="I16" s="4"/>
       <c r="J16" s="4"/>
-    </row>
-    <row r="17" ht="80" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K16" s="4"/>
+    </row>
+    <row r="17" ht="100" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
@@ -682,8 +690,9 @@
       <c r="H17" s="4"/>
       <c r="I17" s="4"/>
       <c r="J17" s="4"/>
-    </row>
-    <row r="18" ht="80" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K17" s="4"/>
+    </row>
+    <row r="18" ht="100" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
@@ -693,8 +702,9 @@
       <c r="H18" s="4"/>
       <c r="I18" s="4"/>
       <c r="J18" s="4"/>
-    </row>
-    <row r="19" ht="80" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K18" s="4"/>
+    </row>
+    <row r="19" ht="100" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
@@ -704,8 +714,9 @@
       <c r="H19" s="4"/>
       <c r="I19" s="4"/>
       <c r="J19" s="4"/>
-    </row>
-    <row r="20" ht="80" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K19" s="4"/>
+    </row>
+    <row r="20" ht="100" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
@@ -715,29 +726,30 @@
       <c r="H20" s="4"/>
       <c r="I20" s="4"/>
       <c r="J20" s="4"/>
-    </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B22" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5"/>
-      <c r="I22" s="5"/>
-      <c r="J22" s="5"/>
+      <c r="K20" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="B2:J2"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="G6:J6"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B22:J22"/>
+  <mergeCells count="18">
+    <mergeCell ref="B2:K2"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="B6:C7"/>
+    <mergeCell ref="D6:G6"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>